--- a/reports/load_report.xlsx
+++ b/reports/load_report.xlsx
@@ -23,7 +23,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:29:47 pm</t>
+    <t>18/6/2026, 1:15:21 pm</t>
   </si>
   <si>
     <t>Test Suite Title</t>
